--- a/RheoBoard_PCB/RheoBoard_v1/CPL/CPL_JLCSMT.xlsx
+++ b/RheoBoard_PCB/RheoBoard_v1/CPL/CPL_JLCSMT.xlsx
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>125.3000mm</t>
+          <t>127.2000mm</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>-53.3700mm</t>
+          <t>-58.7300mm</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
